--- a/db/generator/exports/sample_upload_2.xlsx
+++ b/db/generator/exports/sample_upload_2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,1188 +446,1296 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>37856</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>384</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>151.24</t>
+          <t>74.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>189.75</t>
+          <t>66.82</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>78184</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>759</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>151.2</t>
+          <t>152.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>175.66</t>
+          <t>132.75</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>105113</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>151.21</t>
+          <t>207.22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>231.53</t>
+          <t>119.92</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9726</t>
+          <t>95958</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>151.23</t>
+          <t>206.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>232.45</t>
+          <t>189.72</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9763</t>
+          <t>101267</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>151.23</t>
+          <t>215.96</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>204.07</t>
+          <t>126.42</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9445</t>
+          <t>107922</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>151.22</t>
+          <t>206.26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>227.82</t>
+          <t>181.65</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>109908</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>151.21</t>
+          <t>223.53</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>193.81</t>
+          <t>161.5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>126805</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>151.19</t>
+          <t>229.09</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>207.49</t>
+          <t>179.78</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>112114</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>151.24</t>
+          <t>221.16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>195.46</t>
+          <t>200.19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>125835</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>151.24</t>
+          <t>219.02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>225.51</t>
+          <t>172.78</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>110959</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>151.21</t>
+          <t>211.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>239.78</t>
+          <t>129.64</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>112075</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>151.2</t>
+          <t>214.86</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>221.72</t>
+          <t>137.65</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>108911</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>151.23</t>
+          <t>221.03</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>207.47</t>
+          <t>225.11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>107476</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>151.21</t>
+          <t>216.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>242.17</t>
+          <t>176.38</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>126219</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>151.2</t>
+          <t>216.59</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>272.46</t>
+          <t>117.09</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>96099</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>994</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>151.24</t>
+          <t>212.56</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>170.77</t>
+          <t>185.09</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>106461</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>151.24</t>
+          <t>225.14</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>206.99</t>
+          <t>171.03</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>105844</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>151.23</t>
+          <t>216.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>223.8</t>
+          <t>134.48</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>114149</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>151.19</t>
+          <t>210.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>148.98</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10012</t>
+          <t>100835</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>947</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>151.2</t>
+          <t>205.07</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>299.57</t>
+          <t>184.85</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>109643</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>151.19</t>
+          <t>213.05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>283.3</t>
+          <t>175.49</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10897</t>
+          <t>104488</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2589</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>151.24</t>
+          <t>209.05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>196.22</t>
+          <t>130.47</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9774</t>
+          <t>106308</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>151.22</t>
+          <t>218.16</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>165.35</t>
+          <t>146.78</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9078</t>
+          <t>114585</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>151.2</t>
+          <t>227.66</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>180.34</t>
+          <t>115.69</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>97501</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2450</t>
+          <t>945</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>151.24</t>
+          <t>206.34</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>222.61</t>
+          <t>142.71</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>9541</t>
+          <t>113724</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>151.21</t>
+          <t>209.29</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>216.32</t>
+          <t>114.28</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11537</t>
+          <t>97200</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>151.24</t>
+          <t>222.33</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>240.8</t>
+          <t>142.01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>122079</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>151.23</t>
+          <t>218.61</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>192.52</t>
+          <t>162.52</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>9384</t>
+          <t>103432</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>151.19</t>
+          <t>221.45</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>171.91</t>
+          <t>145.96</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>95414</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>151.2</t>
+          <t>208.25</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>192.22</t>
+          <t>152.82</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>110652</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>151.22</t>
+          <t>215.15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>185.56</t>
+          <t>150.89</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10049</t>
+          <t>111062</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>151.23</t>
+          <t>212.69</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>215.45</t>
+          <t>109.67</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10884</t>
+          <t>110776</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>151.24</t>
+          <t>222.62</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>205.12</t>
+          <t>111.71</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>105404</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>151.19</t>
+          <t>217.58</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>249.27</t>
+          <t>143.04</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>105173</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>151.22</t>
+          <t>215.52</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>204.32</t>
+          <t>145.62</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>106772</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2463</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>151.24</t>
+          <t>222.74</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>129.57</t>
+          <t>126.86</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>105496</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>151.18</t>
+          <t>216.43</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>142.6</t>
+          <t>139.72</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>109665</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>151.24</t>
+          <t>226.06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>176.75</t>
+          <t>144.15</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10185</t>
+          <t>102276</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>151.23</t>
+          <t>232.32</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>204.9</t>
+          <t>143.19</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11177</t>
+          <t>115458</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>151.22</t>
+          <t>232.01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>208.36</t>
+          <t>88.78</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>9272</t>
+          <t>117140</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>151.24</t>
+          <t>215.16</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>179.48</t>
+          <t>102.48</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>102680</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>151.2</t>
+          <t>211.7</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>193.7</t>
+          <t>117.19</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9621</t>
+          <t>103660</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>151.23</t>
+          <t>221.88</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>166.72</t>
+          <t>133.13</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>105618</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>151.22</t>
+          <t>209.01</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>83.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>112059</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>217.14</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>87.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>134571</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>229.65</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>116.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>126701</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>223.42</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>81.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>103732</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>217.99</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>106.97</t>
         </is>
       </c>
     </row>
